--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ40"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1376,48 +1376,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135710601</v>
+        <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93390</v>
+        <v>93426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Jonkmyrliden, Vb</t>
+          <t>Fromheden, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712964</v>
+        <v>712515</v>
       </c>
       <c r="R8" t="n">
-        <v>7218995</v>
+        <v>7219057</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,27 +1445,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Bild</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,28 +1480,24 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710601</t>
+          <t>https://artportalen.se/Sighting/137153507</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135710622</v>
+        <v>135710601</v>
       </c>
       <c r="B9" t="n">
         <v>93390</v>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712868</v>
+        <v>712964</v>
       </c>
       <c r="R9" t="n">
-        <v>7219096</v>
+        <v>7218995</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,7 +1577,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,38 +1612,38 @@
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710622</t>
+          <t>https://artportalen.se/Sighting/135710601</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135710604</v>
+        <v>135710622</v>
       </c>
       <c r="B10" t="n">
-        <v>93075</v>
+        <v>93390</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4787</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712999</v>
+        <v>712868</v>
       </c>
       <c r="R10" t="n">
-        <v>7219045</v>
+        <v>7219096</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1693,12 +1698,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Bilder</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,16 +1728,16 @@
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710604</t>
+          <t>https://artportalen.se/Sighting/135710622</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135710625</v>
+        <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>79217</v>
+        <v>93438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,37 +1745,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Jonkmyrliden, Vb</t>
+          <t>Fromheden, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712692</v>
+        <v>712685</v>
       </c>
       <c r="R11" t="n">
-        <v>7219138</v>
+        <v>7219111</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1799,22 +1803,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,53 +1838,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710625</t>
+          <t>https://artportalen.se/Sighting/137153342</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135710602</v>
+        <v>135710604</v>
       </c>
       <c r="B12" t="n">
-        <v>80079</v>
+        <v>93075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,10 +1890,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712982</v>
+        <v>712999</v>
       </c>
       <c r="R12" t="n">
-        <v>7219029</v>
+        <v>7219045</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1920,7 +1925,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1935,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bilder</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,16 +1970,16 @@
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710602</t>
+          <t>https://artportalen.se/Sighting/135710604</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135710623</v>
+        <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>80079</v>
+        <v>92149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,37 +1987,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Jonkmyrliden, Vb</t>
+          <t>Fromheden, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712765</v>
+        <v>712647</v>
       </c>
       <c r="R13" t="n">
-        <v>7219116</v>
+        <v>7219117</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2031,22 +2045,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,31 +2080,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710623</t>
+          <t>https://artportalen.se/Sighting/137153316</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135710627</v>
+        <v>135710625</v>
       </c>
       <c r="B14" t="n">
-        <v>80079</v>
+        <v>79217</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,21 +2108,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2192,13 +2207,13 @@
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710627</t>
+          <t>https://artportalen.se/Sighting/135710625</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135710631</v>
+        <v>135710602</v>
       </c>
       <c r="B15" t="n">
         <v>80079</v>
@@ -2233,10 +2248,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712616</v>
+        <v>712982</v>
       </c>
       <c r="R15" t="n">
-        <v>7219141</v>
+        <v>7219029</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2268,7 +2283,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2278,7 +2293,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2308,38 +2323,38 @@
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710631</t>
+          <t>https://artportalen.se/Sighting/135710602</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135710612</v>
+        <v>135710623</v>
       </c>
       <c r="B16" t="n">
-        <v>80580</v>
+        <v>80079</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2349,10 +2364,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712985</v>
+        <v>712765</v>
       </c>
       <c r="R16" t="n">
-        <v>7219079</v>
+        <v>7219116</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2384,7 +2399,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2394,7 +2409,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2424,16 +2439,16 @@
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710612</t>
+          <t>https://artportalen.se/Sighting/135710623</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135710629</v>
+        <v>135710627</v>
       </c>
       <c r="B17" t="n">
-        <v>78464</v>
+        <v>80079</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2441,21 +2456,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2465,10 +2480,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712616</v>
+        <v>712692</v>
       </c>
       <c r="R17" t="n">
-        <v>7219141</v>
+        <v>7219138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2500,7 +2515,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2510,7 +2525,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2540,16 +2555,16 @@
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710629</t>
+          <t>https://artportalen.se/Sighting/135710627</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135710595</v>
+        <v>135710631</v>
       </c>
       <c r="B18" t="n">
-        <v>57993</v>
+        <v>80079</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2557,21 +2572,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2581,10 +2596,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712708</v>
+        <v>712616</v>
       </c>
       <c r="R18" t="n">
-        <v>7218980</v>
+        <v>7219141</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2616,7 +2631,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,12 +2641,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,56 +2671,51 @@
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710595</t>
+          <t>https://artportalen.se/Sighting/135710631</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135710597</v>
+        <v>135710612</v>
       </c>
       <c r="B19" t="n">
-        <v>57993</v>
+        <v>80580</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jonkmyrliden, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712837</v>
+        <v>712985</v>
       </c>
       <c r="R19" t="n">
-        <v>7218940</v>
+        <v>7219079</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2742,7 +2747,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2752,12 +2757,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:52</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2787,16 +2787,16 @@
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710597</t>
+          <t>https://artportalen.se/Sighting/135710612</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135710633</v>
+        <v>135710629</v>
       </c>
       <c r="B20" t="n">
-        <v>57993</v>
+        <v>78464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,42 +2804,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Jonkmyrliden, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712625</v>
+        <v>712616</v>
       </c>
       <c r="R20" t="n">
-        <v>7219023</v>
+        <v>7219141</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2871,7 +2863,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2881,12 +2873,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2916,13 +2903,13 @@
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710633</t>
+          <t>https://artportalen.se/Sighting/135710629</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135710634</v>
+        <v>135710595</v>
       </c>
       <c r="B21" t="n">
         <v>57993</v>
@@ -2951,21 +2938,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Jonkmyrliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712651</v>
+        <v>712708</v>
       </c>
       <c r="R21" t="n">
-        <v>7219020</v>
+        <v>7218980</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2997,7 +2979,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3007,7 +2989,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3042,13 +3024,13 @@
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710634</t>
+          <t>https://artportalen.se/Sighting/135710595</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135710635</v>
+        <v>135710597</v>
       </c>
       <c r="B22" t="n">
         <v>57993</v>
@@ -3088,10 +3070,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712484</v>
+        <v>712837</v>
       </c>
       <c r="R22" t="n">
-        <v>7219068</v>
+        <v>7218940</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3123,7 +3105,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3133,7 +3115,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3168,16 +3150,16 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710635</t>
+          <t>https://artportalen.se/Sighting/135710597</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135710594</v>
+        <v>135710633</v>
       </c>
       <c r="B23" t="n">
-        <v>58154</v>
+        <v>57993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3185,39 +3167,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jonkmyrliden, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712734</v>
+        <v>712625</v>
       </c>
       <c r="R23" t="n">
-        <v>7218999</v>
+        <v>7219023</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3249,7 +3234,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3259,12 +3244,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Läten</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3294,16 +3279,16 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710594</t>
+          <t>https://artportalen.se/Sighting/135710633</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135710596</v>
+        <v>135710634</v>
       </c>
       <c r="B24" t="n">
-        <v>58154</v>
+        <v>57993</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3311,27 +3296,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3340,10 +3325,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712780</v>
+        <v>712651</v>
       </c>
       <c r="R24" t="n">
-        <v>7218966</v>
+        <v>7219020</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3375,7 +3360,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3385,12 +3370,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Läten, flera individer</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3420,16 +3405,16 @@
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710596</t>
+          <t>https://artportalen.se/Sighting/135710634</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135710615</v>
+        <v>135710635</v>
       </c>
       <c r="B25" t="n">
-        <v>58154</v>
+        <v>57993</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3437,27 +3422,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3466,10 +3451,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712979</v>
+        <v>712484</v>
       </c>
       <c r="R25" t="n">
-        <v>7219065</v>
+        <v>7219068</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3501,7 +3486,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3511,12 +3496,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Flera st läten</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3546,13 +3531,13 @@
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710615</t>
+          <t>https://artportalen.se/Sighting/135710635</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135710619</v>
+        <v>135710594</v>
       </c>
       <c r="B26" t="n">
         <v>58154</v>
@@ -3592,10 +3577,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712932</v>
+        <v>712734</v>
       </c>
       <c r="R26" t="n">
-        <v>7219074</v>
+        <v>7218999</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3627,7 +3612,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3637,12 +3622,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Läten flera</t>
+          <t>Läten</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3672,13 +3657,13 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710619</t>
+          <t>https://artportalen.se/Sighting/135710594</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135710621</v>
+        <v>135710596</v>
       </c>
       <c r="B27" t="n">
         <v>58154</v>
@@ -3718,10 +3703,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>712868</v>
+        <v>712780</v>
       </c>
       <c r="R27" t="n">
-        <v>7219079</v>
+        <v>7218966</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3753,7 +3738,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3763,7 +3748,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Läten, flera individer</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3793,51 +3783,56 @@
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710621</t>
+          <t>https://artportalen.se/Sighting/135710596</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135710608</v>
+        <v>135710615</v>
       </c>
       <c r="B28" t="n">
-        <v>99328</v>
+        <v>58154</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jonkmyrliden, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>713015</v>
+        <v>712979</v>
       </c>
       <c r="R28" t="n">
-        <v>7219051</v>
+        <v>7219065</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3869,7 +3864,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3879,12 +3874,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Stor förekomst, många blommande och överblommade ex</t>
+          <t>Flera st läten</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3914,51 +3909,56 @@
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710608</t>
+          <t>https://artportalen.se/Sighting/135710615</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135710610</v>
+        <v>135710619</v>
       </c>
       <c r="B29" t="n">
-        <v>99328</v>
+        <v>58154</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Jonkmyrliden, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>713006</v>
+        <v>712932</v>
       </c>
       <c r="R29" t="n">
-        <v>7219049</v>
+        <v>7219074</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4000,7 +4000,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Läten flera</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4030,51 +4035,56 @@
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710610</t>
+          <t>https://artportalen.se/Sighting/135710619</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135710618</v>
+        <v>135710621</v>
       </c>
       <c r="B30" t="n">
-        <v>99328</v>
+        <v>58154</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jonkmyrliden, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712972</v>
+        <v>712868</v>
       </c>
       <c r="R30" t="n">
-        <v>7219075</v>
+        <v>7219079</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4106,7 +4116,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4116,7 +4126,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4146,38 +4156,38 @@
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710618</t>
+          <t>https://artportalen.se/Sighting/135710621</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135710611</v>
+        <v>135710608</v>
       </c>
       <c r="B31" t="n">
-        <v>99350</v>
+        <v>99328</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4187,10 +4197,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712985</v>
+        <v>713015</v>
       </c>
       <c r="R31" t="n">
-        <v>7219079</v>
+        <v>7219051</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4222,7 +4232,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4232,7 +4242,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Stor förekomst, många blommande och överblommade ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4262,38 +4277,38 @@
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710611</t>
+          <t>https://artportalen.se/Sighting/135710608</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135710616</v>
+        <v>135710610</v>
       </c>
       <c r="B32" t="n">
-        <v>99350</v>
+        <v>99328</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4303,10 +4318,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712972</v>
+        <v>713006</v>
       </c>
       <c r="R32" t="n">
-        <v>7219075</v>
+        <v>7219049</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4338,7 +4353,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4348,7 +4363,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4378,38 +4393,38 @@
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710616</t>
+          <t>https://artportalen.se/Sighting/135710610</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135710606</v>
+        <v>135710618</v>
       </c>
       <c r="B33" t="n">
-        <v>99134</v>
+        <v>99328</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223049</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4419,10 +4434,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>713006</v>
+        <v>712972</v>
       </c>
       <c r="R33" t="n">
-        <v>7219037</v>
+        <v>7219075</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4454,7 +4469,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4464,7 +4479,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4494,16 +4509,16 @@
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710606</t>
+          <t>https://artportalen.se/Sighting/135710618</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135710613</v>
+        <v>135710611</v>
       </c>
       <c r="B34" t="n">
-        <v>99134</v>
+        <v>99350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4511,21 +4526,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>223049</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4570,7 +4585,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4580,7 +4595,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4610,38 +4625,38 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710613</t>
+          <t>https://artportalen.se/Sighting/135710611</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135710626</v>
+        <v>135710616</v>
       </c>
       <c r="B35" t="n">
-        <v>79218</v>
+        <v>99350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4651,10 +4666,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>712692</v>
+        <v>712972</v>
       </c>
       <c r="R35" t="n">
-        <v>7219138</v>
+        <v>7219075</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4686,7 +4701,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4696,7 +4711,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4726,38 +4741,38 @@
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710626</t>
+          <t>https://artportalen.se/Sighting/135710616</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135710628</v>
+        <v>135710606</v>
       </c>
       <c r="B36" t="n">
-        <v>79218</v>
+        <v>99134</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>223049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4767,10 +4782,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712637</v>
+        <v>713006</v>
       </c>
       <c r="R36" t="n">
-        <v>7219135</v>
+        <v>7219037</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4802,7 +4817,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4812,7 +4827,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4842,38 +4857,38 @@
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710628</t>
+          <t>https://artportalen.se/Sighting/135710606</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135710630</v>
+        <v>135710613</v>
       </c>
       <c r="B37" t="n">
-        <v>79218</v>
+        <v>99134</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>223049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4883,10 +4898,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712616</v>
+        <v>712985</v>
       </c>
       <c r="R37" t="n">
-        <v>7219141</v>
+        <v>7219079</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4918,7 +4933,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4928,7 +4943,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4958,16 +4973,16 @@
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710630</t>
+          <t>https://artportalen.se/Sighting/135710613</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135710607</v>
+        <v>135710626</v>
       </c>
       <c r="B38" t="n">
-        <v>80050</v>
+        <v>79218</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4975,21 +4990,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4999,10 +5014,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>713004</v>
+        <v>712692</v>
       </c>
       <c r="R38" t="n">
-        <v>7219026</v>
+        <v>7219138</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5034,7 +5049,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5044,7 +5059,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5074,16 +5089,16 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710607</t>
+          <t>https://artportalen.se/Sighting/135710626</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135710624</v>
+        <v>135710628</v>
       </c>
       <c r="B39" t="n">
-        <v>80050</v>
+        <v>79218</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5091,21 +5106,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5115,7 +5130,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>712708</v>
+        <v>712637</v>
       </c>
       <c r="R39" t="n">
         <v>7219135</v>
@@ -5150,7 +5165,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5160,7 +5175,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5190,16 +5205,16 @@
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135710624</t>
+          <t>https://artportalen.se/Sighting/135710628</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135710632</v>
+        <v>135710630</v>
       </c>
       <c r="B40" t="n">
-        <v>79483</v>
+        <v>79218</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5207,21 +5222,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5231,10 +5246,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>712610</v>
+        <v>712616</v>
       </c>
       <c r="R40" t="n">
-        <v>7219117</v>
+        <v>7219141</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5266,7 +5281,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5276,7 +5291,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5305,6 +5320,354 @@
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710630</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135710607</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Jonkmyrliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>713004</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7219026</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710607</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135710624</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80050</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Jonkmyrliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>712708</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7219135</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135710624</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135710632</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Jonkmyrliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>712610</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7219117</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135710632</t>
         </is>
@@ -5351,6 +5714,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -1379,7 +1379,7 @@
         <v>137153507</v>
       </c>
       <c r="B8" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>137153342</v>
       </c>
       <c r="B11" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137153316</v>
       </c>
       <c r="B13" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
